--- a/BDD_Corpus/Columnas de opinión - Semana - 2019.xlsx
+++ b/BDD_Corpus/Columnas de opinión - Semana - 2019.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karen\Documents\HumanidadesDigitales_git\BDD_Corpus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110AD8F1-F5E9-4476-937C-E5C16DE87064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86607192-A5F9-4E87-A857-C3CF6D04615A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6CFE94E-F08C-1746-9DE1-D02FC6EF12E7}"/>
   </bookViews>
@@ -15430,6 +15430,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ed9ac0ff-2c52-4327-b8dc-86996d56a004" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="247c4332-1be9-42a8-ac54-bce5b9c133e1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E9B572BCF508FA46A82D2555325F121D" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="01cdcfdf8f082fc3a4be4916e6ea18b2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="247c4332-1be9-42a8-ac54-bce5b9c133e1" xmlns:ns3="ed9ac0ff-2c52-4327-b8dc-86996d56a004" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54d3e4d9209e80f1068dae6dcca34293" ns2:_="" ns3:_="">
     <xsd:import namespace="247c4332-1be9-42a8-ac54-bce5b9c133e1"/>
@@ -15630,42 +15650,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ed9ac0ff-2c52-4327-b8dc-86996d56a004" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="247c4332-1be9-42a8-ac54-bce5b9c133e1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCF68ACC-9F18-44DA-91FE-EA73C9D36EDC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6FA636B-AD3A-4E14-9084-34106BB418D4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="247c4332-1be9-42a8-ac54-bce5b9c133e1"/>
-    <ds:schemaRef ds:uri="ed9ac0ff-2c52-4327-b8dc-86996d56a004"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15684,9 +15672,21 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6FA636B-AD3A-4E14-9084-34106BB418D4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCF68ACC-9F18-44DA-91FE-EA73C9D36EDC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="247c4332-1be9-42a8-ac54-bce5b9c133e1"/>
+    <ds:schemaRef ds:uri="ed9ac0ff-2c52-4327-b8dc-86996d56a004"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>